--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -909,35 +909,35 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +478,6609 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Accounts Payable Lead</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4865187101?gh_jid=4865187101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer -  3D Computer Vision</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4911999101?gh_jid=4911999101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - AI Safety</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4334849101?gh_jid=4334849101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer -  Computer Vision</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4334842101?gh_jid=4334842101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - Foundation Models</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4766708101?gh_jid=4766708101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - GPU Simulation</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin - London - Paris</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4953387101?gh_jid=4953387101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - ML Engineering</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4778869101?gh_jid=4778869101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - ML &amp; Signal Processing</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4372802101?gh_jid=4372802101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona; Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4676357101?gh_jid=4676357101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Intern (PhD) – 3D Computer Vision</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona; Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4941957101?gh_jid=4941957101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Associate Programme Manager - Land</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4944070101?gh_jid=4944070101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Avionics Hardware Engineer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4878635101?gh_jid=4878635101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camera Engineer </t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4939591101?gh_jid=4939591101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4516967101?gh_jid=4516967101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Design Engineer - Electronics</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4660594101?gh_jid=4660594101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Drone Field Engineer</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4390825101?gh_jid=4390825101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Finance Data Engineer</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4871604101?gh_jid=4871604101</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Head of FP&amp;A</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4963307101?gh_jid=4963307101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsing – Formula Student Programme </t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4865788101?gh_jid=4865788101</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>HPC Systems Administrator</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4879386101?gh_jid=4879386101</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Incoming Inspector - Production Quality</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4861198101?gh_jid=4861198101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead Engineer – Ground Control Station (GCS) &amp; Hardware Simulator </t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4899205101?gh_jid=4899205101</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Lead Legal Counsel Corporate Office</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4934651101?gh_jid=4934651101</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Active RF Sensing</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4900888101?gh_jid=4900888101</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead Systems Engineer - Avionics Communication </t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4879138101?gh_jid=4879138101</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - EO/IR Sensing</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4782393101?gh_jid=4782393101</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - LO Emission Control &amp; RF Interoperability</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4782354101?gh_jid=4782354101</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Low Observability Shaping &amp; Materials</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4844205101?gh_jid=4844205101</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Maritime</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4908213101?gh_jid=4908213101</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer – Military Communications</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924405101?gh_jid=4924405101</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Passive RF Sensing</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4888238101?gh_jid=4888238101</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Legal Counsel Contracts &amp; Commercial</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4934633101?gh_jid=4934633101</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LSA Engineer </t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4948287101?gh_jid=4948287101</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A Integration Manager</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4878160101?gh_jid=4878160101</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multimodal Sensing and Fusion Engineer </t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4938743101?gh_jid=4938743101</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multimodal Sensing Test Engineer </t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4947489101?gh_jid=4947489101</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obsolescence Manager </t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4948277101?gh_jid=4948277101</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Payroll Specialist</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4876698101?gh_jid=4876698101</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>People Business Partner - Munich</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4841774101?gh_jid=4841774101</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Process &amp; Internal Control System Lead</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4871611101?gh_jid=4871611101</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement Manager – Tech &amp; IT </t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4959374101?gh_jid=4959374101</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin - London - Paris</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4564710101?gh_jid=4564710101</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Production Engineer - Software Integration</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4788891101?gh_jid=4788891101</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager — Electronic Warfare (Offboard &amp; Cross-Platform)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4869481101?gh_jid=4869481101</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme Manager </t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4636978101?gh_jid=4636978101</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager - Land</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4944089101?gh_jid=4944089101</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager - Space</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4942502101?gh_jid=4942502101</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Assurance Engineer - Development </t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4872445101?gh_jid=4872445101</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Radio Engineer</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4921704101?gh_jid=4921704101</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional Sales Lead, DACH - Land </t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4954531101?gh_jid=4954531101</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF &amp; EMC Engineer </t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4878616101?gh_jid=4878616101</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safety Manager (System Safety) </t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4948063101?gh_jid=4948063101</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Senior Accountant</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4927641101?gh_jid=4927641101</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Senior CAPEX &amp; Fixed Assets Accountant</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4928128101?gh_jid=4928128101</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Commercial Finance Business Partner </t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4963868101?gh_jid=4963868101</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Senior Commercial Manager - Air</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4880212101?gh_jid=4880212101</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Senior Industrial Designer</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4878760101?gh_jid=4878760101</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Inventory Accountant </t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4928133101?gh_jid=4928133101</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Lead Engineer Electronic Warfare and Survivability </t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4870670101?gh_jid=4870670101</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>London; Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4468911101?gh_jid=4468911101</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager - Integrated Logistics Support</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4913312101?gh_jid=4913312101</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Land</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4944213101?gh_jid=4944213101</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Maritime</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4875025101?gh_jid=4875025101</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Militarisation</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4913364101?gh_jid=4913364101</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager Mission Systems</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4968741101?gh_jid=4968741101</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager – Physical Products</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4880207101?gh_jid=4880207101</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Systems Engineer – EA Antenna &amp; Payload Design </t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924427101?gh_jid=4924427101</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer ESM / ELS</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924407101?gh_jid=4924407101</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Systems Safety Engineer - Air</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4776546101?gh_jid=4776546101</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Systems Safety Engineer - Land</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924017101?gh_jid=4924017101</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Senior Talent Acquisition Partner</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4912850101?gh_jid=4912850101</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Simulation Engineer</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4948430101?gh_jid=4948430101</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4347030101?gh_jid=4347030101</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4737931101?gh_jid=4737931101</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Airborne Mission Systems</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741565101?gh_jid=4741565101</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Autonomous Air Systems</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741571101?gh_jid=4741571101</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Autonomous Air System V&amp;V</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741219101?gh_jid=4741219101</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4125061101?gh_jid=4125061101</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Frontend</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin - London</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4126378101?gh_jid=4126378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Frontend Autonomous Air System V&amp;V</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741224101?gh_jid=4741224101</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Ground to Air HMI</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741242101?gh_jid=4741242101</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff Software Engineer </t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4923741101?gh_jid=4923741101</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Stress &amp; Dynamics Engineer</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4876328101?gh_jid=4876328101</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Systems Architect - Electronic Warfare</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4782364101?gh_jid=4782364101</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer (Avionics)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4902679101?gh_jid=4902679101</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Command and Control (Air)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4787205101?gh_jid=4787205101</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Electromagnetic Interference (EMI)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4865559101?gh_jid=4865559101</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Physical Products</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4839745101?gh_jid=4839745101</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer (Requirements Manager), Aviation</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4871824101?gh_jid=4871824101</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer V&amp;V - Air</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4813822101?gh_jid=4813822101</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Systems Technical Writer</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4876451101?gh_jid=4876451101</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Talent Operations Coordinator - 12-month FTC</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4957296101?gh_jid=4957296101</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Technical Lead Engineer, UAV Development</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4888975101?gh_jid=4888975101</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Technical Logistical Support (TLB) Manager</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4948293101?gh_jid=4948293101</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager - Air</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4865991101?gh_jid=4865991101</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse Clerk </t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4964970101?gh_jid=4964970101</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse Manager</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4965312101?gh_jid=4965312101</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse Operator</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4963213101?gh_jid=4963213101</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Wireless Communications Systems Engineer</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4923845101?gh_jid=4923845101</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Associate Account Executive (Top Talent Sales Program - Lunar)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7816965003?gh_jid=7816965003</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate (AI) Solution Consultant - Orbit Program </t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7814021003?gh_jid=7814021003</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Associate Applied (AI) Value Engineer (DACH) - Orbit Program</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7819725003?gh_jid=7819725003</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Client Account Lead - Strategy &amp; Transformation (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7773301003?gh_jid=7773301003</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Client Account Lead - Strategy &amp; Transformation (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany, Cologne</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820048003?gh_jid=7820048003</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Client Engagement Partner - AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany, Cologne</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820049003?gh_jid=7820049003</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Client Engagement Partner - AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7777097003?gh_jid=7777097003</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany, Duesseldorf</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7694626003?gh_jid=7694626003</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7693390003?gh_jid=7693390003</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner- AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7777096003?gh_jid=7777096003</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr"/>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner- AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany, Cologne</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820050003?gh_jid=7820050003</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr"/>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner - Retail</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7749202003?gh_jid=7749202003</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr"/>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner - Retail</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany, Duesseldorf</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7749204003?gh_jid=7749204003</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr"/>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Client Value Partner - Retail </t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7762257003?gh_jid=7762257003</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr"/>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr"/>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr"/>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise AI Consultant</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7972958003?gh_jid=7972958003</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr"/>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Architect Director</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Zürich, Switzerland</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7693178003?gh_jid=7693178003</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr"/>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Architect Director</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7681585003?gh_jid=7681585003</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr"/>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Executive Briefing Center Lead (Content &amp; Immersive Experience)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7853314003?gh_jid=7853314003</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr"/>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>GSI Partner Lead EMEA</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7773228003?gh_jid=7773228003</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr"/>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Head of Industry - Manufacturing</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/6048490003?gh_jid=6048490003</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr"/>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head of Industry - Retail &amp; CPG </t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/6313858003?gh_jid=6313858003</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr"/>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Innovation Lead (Intrapreneur) - Full-time / Part-time</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7638119003?gh_jid=7638119003</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr"/>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Intern / Working Student Online Training Translation (Korean speaking)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7886106003?gh_jid=7886106003</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Lead Cloud Economics Specialist</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7802410003?gh_jid=7802410003</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr"/>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Lead Deployment Architect</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7727306003?gh_jid=7727306003</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr"/>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Lead Deployment Architect - AI</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7928952003?gh_jid=7928952003</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr"/>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Lead / Principal Consultant - Data and AI</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7926567003?gh_jid=7926567003</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr"/>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Lead / Principal Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683435003?gh_jid=7683435003</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr"/>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Lead/Principal Digital Transformation &amp; Process Optimisation Consultant - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7765927003?gh_jid=7765927003</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr"/>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Lead/Principal Management &amp; Technology Consultant  - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7770069003?gh_jid=7770069003</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr"/>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Lead/Principal Process Intelligence &amp; Supply Chain Transformation Consultant - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7770073003?gh_jid=7770073003</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr"/>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Lead/Principal Value Engineer - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7773834003?gh_jid=7773834003</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr"/>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr"/>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Lead Value Engineer - Insurance</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7828363003?gh_jid=7828363003</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr"/>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Principal Enterprise Architect </t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7539075003?gh_jid=7539075003</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr"/>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Product Lead - Front Office - (CX, Sales, Service Marketing, Commerce)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/5928673003?gh_jid=5928673003</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr"/>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Product Marketing Lead (Executive Briefing Program)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7979275003?gh_jid=7979275003</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr"/>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Application Product Manager - Supply Chain - Procurement </t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7984249003?gh_jid=7984249003</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr"/>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Senior Applied Value Engineer</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7825688003?gh_jid=7825688003</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr"/>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Senior Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Zürich, Switzerland</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7600347003?gh_jid=7600347003</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr"/>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Design Engineer, Design System </t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7799733003?gh_jid=7799733003</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr"/>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7817273003?gh_jid=7817273003</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr"/>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant (Senior Value Engineer) - Scale Team</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7826212003?gh_jid=7826212003</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr"/>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Senior Management &amp; Technology Consultant  - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7825968003?gh_jid=7825968003</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr"/>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7825969003?gh_jid=7825969003</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr"/>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Context Model Core Team</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820412003?gh_jid=7820412003</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr"/>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Senior Value Engineer - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7825970003?gh_jid=7825970003</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr"/>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Senior Value Engineer - Scale Team</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7817387003?gh_jid=7817387003</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr"/>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer - Context Model Core Team</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820430003?gh_jid=7820430003</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr"/>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strategic Account Executive / Client Partner - Manufacturing </t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7607677003?gh_jid=7607677003</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr"/>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strategic Account Executive / Client Partner - Manufacturing </t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7631651003?gh_jid=7631651003</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr"/>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Werktudent/in mit Schwerpunkt Gesellschaftsrecht</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7885744003?gh_jid=7885744003</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr"/>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Working Student Corporate Law Specialist</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7813081003?gh_jid=7813081003</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr"/>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Personio</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>https://personio.jobs.personio.de/job/1834171</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr"/>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Working student – Quality Management</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000146645680</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr"/>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Business Application Engineer – Polarion ALM</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000144263839</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr"/>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent:in Social Media</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000144018092</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr"/>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>IT Support Technician (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000142051419</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr"/>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Working Student Communication &amp; PR </t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000141893804</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr"/>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Area Product Owner Business Development - RT Elements</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000141845300</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr"/>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Working Student - Digital Learning</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000141712000</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr"/>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Corporate Counsel (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000140933859</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr"/>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>(Junior) Technical Project Manager – Events &amp; Exhibits</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000137106040</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr"/>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Senior Group Reporting &amp; Accounting Policies (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000136443709</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr"/>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>HR Payroll Specialist (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000135740449</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr"/>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager - Spine Surgery</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000135719749</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr"/>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>(Junior) Area Account Manager (m/w/d) Schweiz</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Zürich, ch</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000134831479</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr"/>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Senior Accountant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000132183599</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr"/>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Working Student - Mixed Reality Developer (Godot/C++)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000131687160</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr"/>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Manager Product Management - Integrated OR</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000131677110</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr"/>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buchhalter:in  </t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000131677598</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr"/>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Senior) Project Engineer - Surgical Navigation Platforms </t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000129775149</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr"/>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Working Student Digital Learning –  R&amp;D Product Support</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000122441969</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr"/>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Senior) Software Engineer – Radiotherapy Positioning &amp; Monitoring </t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000120639709</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr"/>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Accounting Assistant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000112601494</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr"/>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>TWAICE</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Working Student | Accounting &amp; Finance (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Hybrid</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>https://twaice.jobs.personio.de/job/2779072</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr"/>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Blickfeld</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Initiativbewerbung</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>https://blickfeld.jobs.personio.de/job/128278</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr"/>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Blickfeld</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Mitarbeiter in der Auftrags- und Bestellabwicklung in Teilzeit (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>https://blickfeld.jobs.personio.de/job/2780642</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr"/>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Blickfeld</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent*in / IDP: Software Development (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>https://blickfeld.jobs.personio.de/job/2595961</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr"/>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Analyst (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/c77fe49e-c58d-42bb-8a4a-c0c3517e0e9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr"/>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Working Student – BMS Software Testing (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>...tudent – BMS Software Testing (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/cfa18a3c-71f8-4f84-b28b-0412cdfee5a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr"/>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Product Owner Hardware (Bauteilverantwortliche*r) - (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>...(Bauteilverantwortliche*r) - (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/e722087a-6129-4366-a638-d68814de2e3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr"/>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Engineer (C++) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>...edded Software Engineer (C++) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/6c052597-f8b6-4ed0-b311-a3308998bc2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr"/>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Program Planning Manager - Development  (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>...anning Manager - Development  (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/d820a75d-1486-486f-bcd3-0a02f05b08c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr"/>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Software and System Testing (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>...- Software and System Testing (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/4472cec3-8839-4e87-b9ee-7abe91421589</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr"/>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Development Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Development Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/321bfc57-ff1f-4288-98fc-af59a3d0fdf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr"/>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Senior Supplier Quality Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>...nior Supplier Quality Manager (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/d15c6ed6-1880-4ba9-a9b1-85fc2c371d40</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr"/>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Senior Test Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Senior Test Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/f731d4d8-1f65-45f3-b6ba-e2316adac453</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr"/>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer (C/C++) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>...pal Software Engineer (C/C++) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/5b6595f3-389f-401e-b308-c8f6ae49ddb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr"/>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/ba1a138b-d85a-45ea-b560-e0e7ffcce356</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr"/>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Hardware Design Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>...ior) Hardware Design Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/9fa9670f-6c59-4510-96d8-de7104a23705</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr"/>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Functional Safety &amp; Cybersecurity Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>...afety &amp; Cybersecurity Manager (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/8bf45b4f-ecd1-4143-8ea8-7d5afc9ae8f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr"/>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Working Student – Battery Science and Data (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>...nt – Battery Science and Data (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/01c68b95-023d-476e-8b2d-654b5ffc7581</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr"/>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/e94ef6e0-6c2d-4901-a931-32b772b1bc62</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr"/>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Software Product Owner (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Software Product Owner (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/7a10f170-0636-4601-af80-1923a9af588c</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr"/>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Inhouse Technical Recruiter (temporary contract for 1 year) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>...emporary contract for 1 year) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/51e71582-de42-40b9-ab1c-33cadc119bcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr"/>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Field Application Engineer – Battery Management Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>...– Battery Management Systems (m/f/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/afae4447-3a1a-41d1-b864-dda39992c320</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr"/>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Developer (C) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>...bedded Software Developer (C) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/c14b725d-cfee-4953-95ae-d129cd928ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr"/>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Test System Technician (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Test System Technician (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/44e2b5e8-8734-44e0-9409-56d1c4e2a663</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr"/>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Design Quality Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Design Quality Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/716b8f7a-dc69-41d9-acb2-1ccfd83a4fcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr"/>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>IT Cloud Administrator (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>IT Cloud Administrator (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/1f17fad1-7d8e-4355-9bc3-9aedd7e283c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr"/>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Working Student – Software Development (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>...tudent – Software Development (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/6a466d9a-f1fd-4537-a879-4062857eb8c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr"/>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Putzhilfe/Reinigungskraft (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Putzhilfe/Reinigungskraft (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/bcc4cef8-4e5f-4613-a355-d2b0f30e3bf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr"/>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Hausmeister/Facility Manager Assistant (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>...er/Facility Manager Assistant (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/a3263557-3de5-4760-b353-4750aab7da80</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr"/>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing Technology Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>...facturing Technology Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/e536a980-8091-4c80-9f43-ea3eb9372c1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr"/>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>NPI manager - Product Lifecycle Management (PLM) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>...ct Lifecycle Management (PLM) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/1ea0166b-fd1c-4638-9927-ed448388ea35</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr"/>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Working Student / Intern - Hardware Validation (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>...Intern - Hardware Validation (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/0c10458a-38c3-404d-a923-7c231f781b1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr"/>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Lead Accounting &amp; Tax (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Lead Accounting &amp; Tax (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/28766943-5082-43c4-b983-b413097a5f63</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr"/>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Working Student - Microfactory (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>...orking Student - Microfactory (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/f4d4c43d-d727-48c9-a5e6-ae95e6b16266</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr"/>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head of Program Management (f/m/d) </t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Head of Program Management (f/m/d)  @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/892df0b0-92f4-4587-8a7f-c0c4625831ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr"/>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Technical Lead Hardware Design (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>...echnical Lead Hardware Design (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/c4228b51-a553-45f2-9e32-07adda11a862</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr"/>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Scandit</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Computer Vision Engineer (Action Recognition) </t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.scandit.com/careers/job-description/?gh_jid=7588975</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -482,6603 +482,6390 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Accounts Payable Lead</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4865187101?gh_jid=4865187101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>AI Research Engineer -  3D Computer Vision</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4911999101?gh_jid=4911999101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>AI Research Engineer - AI Safety</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4334849101?gh_jid=4334849101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>AI Research Engineer -  Computer Vision</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4334842101?gh_jid=4334842101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>AI Research Engineer - Foundation Models</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4766708101?gh_jid=4766708101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>AI Research Engineer - GPU Simulation</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich - Berlin - London - Paris</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4953387101?gh_jid=4953387101</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>AI Research Engineer - ML Engineering</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4778869101?gh_jid=4778869101</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>AI Research Engineer - ML &amp; Signal Processing</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4372802101?gh_jid=4372802101</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>AI Research Engineer - Reinforcement Learning</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Barcelona; Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4676357101?gh_jid=4676357101</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>AI Research Intern (PhD) – 3D Computer Vision</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Barcelona; Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4941957101?gh_jid=4941957101</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Associate Programme Manager - Land</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4944070101?gh_jid=4944070101</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Avionics Hardware Engineer</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4878635101?gh_jid=4878635101</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">Camera Engineer </t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4939591101?gh_jid=4939591101</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Deployed AI Engineer</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4516967101?gh_jid=4516967101</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Design Engineer - Electronics</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4660594101?gh_jid=4660594101</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Drone Field Engineer</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4390825101?gh_jid=4390825101</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Finance Data Engineer</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4871604101?gh_jid=4871604101</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Head of FP&amp;A</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4963307101?gh_jid=4963307101</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">Helsing – Formula Student Programme </t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4865788101?gh_jid=4865788101</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>HPC Systems Administrator</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4879386101?gh_jid=4879386101</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Incoming Inspector - Production Quality</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4861198101?gh_jid=4861198101</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">Lead Engineer – Ground Control Station (GCS) &amp; Hardware Simulator </t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="E23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4899205101?gh_jid=4899205101</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Lead Legal Counsel Corporate Office</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="E24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4934651101?gh_jid=4934651101</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Lead Systems Engineer - Active RF Sensing</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="E25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4900888101?gh_jid=4900888101</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">Lead Systems Engineer - Avionics Communication </t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="E26" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4879138101?gh_jid=4879138101</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Lead Systems Engineer - EO/IR Sensing</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4782393101?gh_jid=4782393101</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Lead Systems Engineer - LO Emission Control &amp; RF Interoperability</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4782354101?gh_jid=4782354101</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Lead Systems Engineer - Low Observability Shaping &amp; Materials</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4844205101?gh_jid=4844205101</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Lead Systems Engineer - Maritime</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="E30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4908213101?gh_jid=4908213101</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Lead Systems Engineer – Military Communications</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="E31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4924405101?gh_jid=4924405101</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Lead Systems Engineer - Passive RF Sensing</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="E32" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4888238101?gh_jid=4888238101</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Legal Counsel Contracts &amp; Commercial</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="E33" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4934633101?gh_jid=4934633101</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t xml:space="preserve">LSA Engineer </t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="E34" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4948287101?gh_jid=4948287101</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>M&amp;A Integration Manager</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="E35" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4878160101?gh_jid=4878160101</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">Multimodal Sensing and Fusion Engineer </t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4938743101?gh_jid=4938743101</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">Multimodal Sensing Test Engineer </t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="E37" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4947489101?gh_jid=4947489101</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">Obsolescence Manager </t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="E38" t="n">
+        <v>50</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4948277101?gh_jid=4948277101</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Payroll Specialist</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="E39" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4876698101?gh_jid=4876698101</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>People Business Partner - Munich</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="E40" t="n">
+        <v>50</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4841774101?gh_jid=4841774101</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Process &amp; Internal Control System Lead</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="E41" t="n">
+        <v>50</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4871611101?gh_jid=4871611101</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t xml:space="preserve">Procurement Manager – Tech &amp; IT </t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="E42" t="n">
+        <v>50</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4959374101?gh_jid=4959374101</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Product Designer</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="E43" t="n">
+        <v>50</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Munich - Berlin - London - Paris</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4564710101?gh_jid=4564710101</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Production Engineer - Software Integration</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="E44" t="n">
+        <v>50</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4788891101?gh_jid=4788891101</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Product Manager — Electronic Warfare (Offboard &amp; Cross-Platform)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="E45" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4869481101?gh_jid=4869481101</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t xml:space="preserve">Programme Manager </t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="E46" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4636978101?gh_jid=4636978101</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Programme Manager - Land</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="E47" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4944089101?gh_jid=4944089101</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Programme Manager - Space</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E48" t="n">
+        <v>50</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4942502101?gh_jid=4942502101</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t xml:space="preserve">Quality Assurance Engineer - Development </t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="E49" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4872445101?gh_jid=4872445101</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Radio Engineer</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="E50" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4921704101?gh_jid=4921704101</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t xml:space="preserve">Regional Sales Lead, DACH - Land </t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="E51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4954531101?gh_jid=4954531101</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t xml:space="preserve">RF &amp; EMC Engineer </t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="E52" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4878616101?gh_jid=4878616101</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t xml:space="preserve">Safety Manager (System Safety) </t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="E53" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4948063101?gh_jid=4948063101</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Senior Accountant</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="E54" t="n">
+        <v>50</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4927641101?gh_jid=4927641101</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t xml:space="preserve"> Senior CAPEX &amp; Fixed Assets Accountant</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="E55" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4928128101?gh_jid=4928128101</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Commercial Finance Business Partner </t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="E56" t="n">
+        <v>50</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4963868101?gh_jid=4963868101</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Senior Commercial Manager - Air</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="E57" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4880212101?gh_jid=4880212101</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Senior Industrial Designer</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="E58" t="n">
+        <v>50</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4878760101?gh_jid=4878760101</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Inventory Accountant </t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="E59" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4928133101?gh_jid=4928133101</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Lead Engineer Electronic Warfare and Survivability </t>
         </is>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="E60" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4870670101?gh_jid=4870670101</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>(Senior) Product Marketing Manager</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="E61" t="n">
+        <v>50</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>London; Munich - Berlin</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4468911101?gh_jid=4468911101</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>(Senior) Programme Manager - Integrated Logistics Support</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="E62" t="n">
+        <v>50</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4913312101?gh_jid=4913312101</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>Senior Programme Manager - Land</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="E63" t="n">
+        <v>50</v>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4944213101?gh_jid=4944213101</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>Senior Programme Manager - Maritime</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="E64" t="n">
+        <v>50</v>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4875025101?gh_jid=4875025101</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>Senior Programme Manager - Militarisation</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="E65" t="n">
+        <v>50</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4913364101?gh_jid=4913364101</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>(Senior) Programme Manager Mission Systems</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="E66" t="n">
+        <v>50</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4968741101?gh_jid=4968741101</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>Senior Project Manager – Physical Products</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="E67" t="n">
+        <v>50</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4880207101?gh_jid=4880207101</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Systems Engineer – EA Antenna &amp; Payload Design </t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="E68" t="n">
+        <v>50</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4924427101?gh_jid=4924427101</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>Senior Systems Engineer ESM / ELS</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="E69" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4924407101?gh_jid=4924407101</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>(Senior) Systems Safety Engineer - Air</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="E70" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4776546101?gh_jid=4776546101</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>(Senior) Systems Safety Engineer - Land</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="E71" t="n">
+        <v>50</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4924017101?gh_jid=4924017101</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>Senior Talent Acquisition Partner</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="E72" t="n">
+        <v>50</v>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4912850101?gh_jid=4912850101</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>Simulation Engineer</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="E73" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4948430101?gh_jid=4948430101</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>Site Reliability Engineer</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="E74" t="n">
+        <v>50</v>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4347030101?gh_jid=4347030101</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="E75" t="n">
+        <v>50</v>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4737931101?gh_jid=4737931101</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>Software Engineer - Airborne Mission Systems</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="E76" t="n">
+        <v>50</v>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741565101?gh_jid=4741565101</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>Software Engineer - Autonomous Air Systems</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="E77" t="n">
+        <v>50</v>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741571101?gh_jid=4741571101</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>Software Engineer - Autonomous Air System V&amp;V</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="E78" t="n">
+        <v>50</v>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741219101?gh_jid=4741219101</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>Software Engineer - Backend</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="E79" t="n">
+        <v>50</v>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4125061101?gh_jid=4125061101</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr"/>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>Software Engineer - Frontend</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="E80" t="n">
+        <v>50</v>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Munich - Berlin - London</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4126378101?gh_jid=4126378101</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr"/>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>Software Engineer - Frontend Autonomous Air System V&amp;V</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="E81" t="n">
+        <v>50</v>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741224101?gh_jid=4741224101</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>Software Engineer - Ground to Air HMI</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="E82" t="n">
+        <v>50</v>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741242101?gh_jid=4741242101</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr"/>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t xml:space="preserve">Staff Software Engineer </t>
         </is>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="E83" t="n">
+        <v>50</v>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4923741101?gh_jid=4923741101</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr"/>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>Stress &amp; Dynamics Engineer</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="E84" t="n">
+        <v>50</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4876328101?gh_jid=4876328101</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr"/>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>Systems Architect - Electronic Warfare</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="E85" t="n">
+        <v>50</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4782364101?gh_jid=4782364101</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr"/>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>Systems Engineer (Avionics)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="E86" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4902679101?gh_jid=4902679101</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr"/>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>Systems Engineer - Command and Control (Air)</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="E87" t="n">
+        <v>50</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4787205101?gh_jid=4787205101</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr"/>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>Systems Engineer - Electromagnetic Interference (EMI)</t>
         </is>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="E88" t="n">
+        <v>50</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4865559101?gh_jid=4865559101</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr"/>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>Systems Engineer - Physical Products</t>
         </is>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="E89" t="n">
+        <v>50</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4839745101?gh_jid=4839745101</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr"/>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>Systems Engineer (Requirements Manager), Aviation</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="E90" t="n">
+        <v>50</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4871824101?gh_jid=4871824101</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>Systems Engineer V&amp;V - Air</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="E91" t="n">
+        <v>50</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4813822101?gh_jid=4813822101</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr"/>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>Systems Technical Writer</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="E92" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4876451101?gh_jid=4876451101</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr"/>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
         <is>
           <t>Talent Operations Coordinator - 12-month FTC</t>
         </is>
       </c>
-      <c r="E93" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="E93" t="n">
+        <v>50</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4957296101?gh_jid=4957296101</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr"/>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>Technical Lead Engineer, UAV Development</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="E94" t="n">
+        <v>50</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4888975101?gh_jid=4888975101</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr"/>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>Technical Logistical Support (TLB) Manager</t>
         </is>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="E95" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4948293101?gh_jid=4948293101</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr"/>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>Technical Programme Manager - Air</t>
         </is>
       </c>
-      <c r="E96" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="E96" t="n">
+        <v>50</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4865991101?gh_jid=4865991101</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr"/>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t xml:space="preserve">Warehouse Clerk </t>
         </is>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="E97" t="n">
+        <v>50</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4964970101?gh_jid=4964970101</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr"/>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>Warehouse Manager</t>
         </is>
       </c>
-      <c r="E98" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="E98" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4965312101?gh_jid=4965312101</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr"/>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>Warehouse Operator</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="E99" t="n">
+        <v>50</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4963213101?gh_jid=4963213101</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr"/>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>Wireless Communications Systems Engineer</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="E100" t="n">
+        <v>50</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4923845101?gh_jid=4923845101</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr"/>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>Associate Account Executive (Top Talent Sales Program - Lunar)</t>
         </is>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="E101" t="n">
+        <v>50</v>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7816965003?gh_jid=7816965003</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr"/>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
         <is>
           <t xml:space="preserve">Associate (AI) Solution Consultant - Orbit Program </t>
         </is>
       </c>
-      <c r="E102" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="E102" t="n">
+        <v>50</v>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7814021003?gh_jid=7814021003</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr"/>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
         <is>
           <t>Associate Applied (AI) Value Engineer (DACH) - Orbit Program</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="E103" t="n">
+        <v>50</v>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7819725003?gh_jid=7819725003</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr"/>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
         <is>
           <t>Client Account Lead - Strategy &amp; Transformation (Logistics/Transportation)</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="E104" t="n">
+        <v>50</v>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7773301003?gh_jid=7773301003</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr"/>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>Client Account Lead - Strategy &amp; Transformation (Logistics/Transportation)</t>
         </is>
       </c>
-      <c r="E105" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="E105" t="n">
+        <v>50</v>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Remote, Germany, Cologne</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7820048003?gh_jid=7820048003</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr"/>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
         <is>
           <t>Client Engagement Partner - AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
         </is>
       </c>
-      <c r="E106" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="E106" t="n">
+        <v>50</v>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Remote, Germany, Cologne</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7820049003?gh_jid=7820049003</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr"/>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
         <is>
           <t>Client Engagement Partner - AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="E107" t="n">
+        <v>50</v>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7777097003?gh_jid=7777097003</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr"/>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
         <is>
           <t>Client Value Partner</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="E108" t="n">
+        <v>50</v>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Remote, Germany, Duesseldorf</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7694626003?gh_jid=7694626003</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr"/>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
         <is>
           <t>Client Value Partner</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="E109" t="n">
+        <v>50</v>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7693390003?gh_jid=7693390003</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr"/>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
         <is>
           <t>Client Value Partner- AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="E110" t="n">
+        <v>50</v>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7777096003?gh_jid=7777096003</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr"/>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>Client Value Partner- AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="E111" t="n">
+        <v>50</v>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Remote, Germany, Cologne</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7820050003?gh_jid=7820050003</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr"/>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
         <is>
           <t>Client Value Partner - Retail</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="E112" t="n">
+        <v>50</v>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7749202003?gh_jid=7749202003</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr"/>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
         <is>
           <t>Client Value Partner - Retail</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="E113" t="n">
+        <v>50</v>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Remote, Germany, Duesseldorf</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7749204003?gh_jid=7749204003</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr"/>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
         <is>
           <t xml:space="preserve">Client Value Partner - Retail </t>
         </is>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="E114" t="n">
+        <v>50</v>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7762257003?gh_jid=7762257003</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr"/>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E115" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="E115" t="n">
+        <v>50</v>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr"/>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="E116" t="n">
+        <v>50</v>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr"/>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
         <is>
           <t>Enterprise AI Consultant</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="E117" t="n">
+        <v>50</v>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7972958003?gh_jid=7972958003</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr"/>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>Enterprise Architect Director</t>
         </is>
       </c>
-      <c r="E118" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="E118" t="n">
+        <v>50</v>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>Zürich, Switzerland</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7693178003?gh_jid=7693178003</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr"/>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>Enterprise Architect Director</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="E119" t="n">
+        <v>50</v>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7681585003?gh_jid=7681585003</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr"/>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>Executive Briefing Center Lead (Content &amp; Immersive Experience)</t>
         </is>
       </c>
-      <c r="E120" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="E120" t="n">
+        <v>50</v>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7853314003?gh_jid=7853314003</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr"/>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
         <is>
           <t>GSI Partner Lead EMEA</t>
         </is>
       </c>
-      <c r="E121" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="E121" t="n">
+        <v>50</v>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7773228003?gh_jid=7773228003</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr"/>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t>Head of Industry - Manufacturing</t>
         </is>
       </c>
-      <c r="E122" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="E122" t="n">
+        <v>50</v>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/6048490003?gh_jid=6048490003</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr"/>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
         <is>
           <t xml:space="preserve">Head of Industry - Retail &amp; CPG </t>
         </is>
       </c>
-      <c r="E123" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="E123" t="n">
+        <v>50</v>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/6313858003?gh_jid=6313858003</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr"/>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
         <is>
           <t>Innovation Lead (Intrapreneur) - Full-time / Part-time</t>
         </is>
       </c>
-      <c r="E124" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="E124" t="n">
+        <v>50</v>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7638119003?gh_jid=7638119003</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr"/>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>Intern / Working Student Online Training Translation (Korean speaking)</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="E125" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7886106003?gh_jid=7886106003</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr"/>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
         <is>
           <t>Lead Cloud Economics Specialist</t>
         </is>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="E126" t="n">
+        <v>50</v>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7802410003?gh_jid=7802410003</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr"/>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
         <is>
           <t>Lead Deployment Architect</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="E127" t="n">
+        <v>50</v>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7727306003?gh_jid=7727306003</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr"/>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>Lead Deployment Architect - AI</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="E128" t="n">
+        <v>50</v>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7928952003?gh_jid=7928952003</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr"/>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
         <is>
           <t>Lead / Principal Consultant - Data and AI</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="E129" t="n">
+        <v>50</v>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7926567003?gh_jid=7926567003</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr"/>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
         <is>
           <t>Lead / Principal Deployment Engineer</t>
         </is>
       </c>
-      <c r="E130" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="E130" t="n">
+        <v>50</v>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683435003?gh_jid=7683435003</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr"/>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
         <is>
           <t>Lead/Principal Digital Transformation &amp; Process Optimisation Consultant - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="E131" t="n">
+        <v>50</v>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7765927003?gh_jid=7765927003</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr"/>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
         <is>
           <t>Lead/Principal Management &amp; Technology Consultant  - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="E132" t="n">
+        <v>50</v>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7770069003?gh_jid=7770069003</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr"/>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
         <is>
           <t>Lead/Principal Process Intelligence &amp; Supply Chain Transformation Consultant - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E133" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="E133" t="n">
+        <v>50</v>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7770073003?gh_jid=7770073003</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr"/>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
         <is>
           <t>Lead/Principal Value Engineer - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E134" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="E134" t="n">
+        <v>50</v>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7773834003?gh_jid=7773834003</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr"/>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E135" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="E135" t="n">
+        <v>50</v>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr"/>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>Lead Value Engineer - Insurance</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="E136" t="n">
+        <v>50</v>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7828363003?gh_jid=7828363003</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr"/>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t xml:space="preserve">Principal Enterprise Architect </t>
         </is>
       </c>
-      <c r="E137" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="E137" t="n">
+        <v>50</v>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7539075003?gh_jid=7539075003</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr"/>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
         <is>
           <t>Product Lead - Front Office - (CX, Sales, Service Marketing, Commerce)</t>
         </is>
       </c>
-      <c r="E138" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="E138" t="n">
+        <v>50</v>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/5928673003?gh_jid=5928673003</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr"/>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
         <is>
           <t>Product Marketing Lead (Executive Briefing Program)</t>
         </is>
       </c>
-      <c r="E139" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="E139" t="n">
+        <v>50</v>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7979275003?gh_jid=7979275003</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr"/>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Application Product Manager - Supply Chain - Procurement </t>
         </is>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="E140" t="n">
+        <v>50</v>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7984249003?gh_jid=7984249003</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr"/>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
         <is>
           <t>Senior Applied Value Engineer</t>
         </is>
       </c>
-      <c r="E141" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="E141" t="n">
+        <v>50</v>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7825688003?gh_jid=7825688003</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr"/>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>Senior Deployment Engineer</t>
         </is>
       </c>
-      <c r="E142" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="E142" t="n">
+        <v>50</v>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Zürich, Switzerland</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7600347003?gh_jid=7600347003</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr"/>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Design Engineer, Design System </t>
         </is>
       </c>
-      <c r="E143" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="E143" t="n">
+        <v>50</v>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7799733003?gh_jid=7799733003</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr"/>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
         <is>
           <t>Senior Digital Transformation &amp; Process Optimisation Consultant - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E144" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="E144" t="n">
+        <v>50</v>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7817273003?gh_jid=7817273003</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr"/>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
         <is>
           <t>Senior Digital Transformation &amp; Process Optimisation Consultant (Senior Value Engineer) - Scale Team</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="E145" t="n">
+        <v>50</v>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7826212003?gh_jid=7826212003</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr"/>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
         <is>
           <t>Senior Management &amp; Technology Consultant  - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E146" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="E146" t="n">
+        <v>50</v>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7825968003?gh_jid=7825968003</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr"/>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
         <is>
           <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E147" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="E147" t="n">
+        <v>50</v>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7825969003?gh_jid=7825969003</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr"/>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
         <is>
           <t>Senior Software Engineer - Context Model Core Team</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="E148" t="n">
+        <v>50</v>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7820412003?gh_jid=7820412003</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr"/>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
         <is>
           <t>Senior Value Engineer - Manufacturing/Production</t>
         </is>
       </c>
-      <c r="E149" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="E149" t="n">
+        <v>50</v>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7825970003?gh_jid=7825970003</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr"/>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
         <is>
           <t>Senior Value Engineer - Scale Team</t>
         </is>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="E150" t="n">
+        <v>50</v>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7817387003?gh_jid=7817387003</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr"/>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
         <is>
           <t>Staff Software Engineer - Context Model Core Team</t>
         </is>
       </c>
-      <c r="E151" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="E151" t="n">
+        <v>50</v>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7820430003?gh_jid=7820430003</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr"/>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
         <is>
           <t xml:space="preserve">Strategic Account Executive / Client Partner - Manufacturing </t>
         </is>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="E152" t="n">
+        <v>50</v>
+      </c>
+      <c r="F152" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7607677003?gh_jid=7607677003</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr"/>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
         <is>
           <t xml:space="preserve">Strategic Account Executive / Client Partner - Manufacturing </t>
         </is>
       </c>
-      <c r="E153" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="E153" t="n">
+        <v>50</v>
+      </c>
+      <c r="F153" t="inlineStr">
         <is>
           <t>Remote, Germany</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7631651003?gh_jid=7631651003</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr"/>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
         <is>
           <t>Werktudent/in mit Schwerpunkt Gesellschaftsrecht</t>
         </is>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="E154" t="n">
+        <v>50</v>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7885744003?gh_jid=7885744003</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr"/>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
         <is>
           <t>Working Student Corporate Law Specialist</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="E155" t="n">
+        <v>50</v>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7813081003?gh_jid=7813081003</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr"/>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Personio</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
         <is>
           <t>Staff Software Engineer, Data Platform</t>
         </is>
       </c>
-      <c r="E156" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="E156" t="n">
+        <v>50</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://personio.jobs.personio.de/job/1834171</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr"/>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
         <is>
           <t>Working student – Quality Management</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="E157" t="n">
+        <v>50</v>
+      </c>
+      <c r="F157" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000146645680</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr"/>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
         <is>
           <t>(Senior) Business Application Engineer – Polarion ALM</t>
         </is>
       </c>
-      <c r="E158" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="E158" t="n">
+        <v>50</v>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000144263839</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr"/>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
         <is>
           <t>Werkstudent:in Social Media</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="E159" t="n">
+        <v>50</v>
+      </c>
+      <c r="F159" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000144018092</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr"/>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
         <is>
           <t>IT Support Technician (m/w/d)</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="E160" t="n">
+        <v>50</v>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000142051419</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr"/>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
         <is>
           <t xml:space="preserve">Working Student Communication &amp; PR </t>
         </is>
       </c>
-      <c r="E161" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="E161" t="n">
+        <v>50</v>
+      </c>
+      <c r="F161" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000141893804</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr"/>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
         <is>
           <t>Area Product Owner Business Development - RT Elements</t>
         </is>
       </c>
-      <c r="E162" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="E162" t="n">
+        <v>50</v>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000141845300</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr"/>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
         <is>
           <t>Working Student - Digital Learning</t>
         </is>
       </c>
-      <c r="E163" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="E163" t="n">
+        <v>50</v>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000141712000</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr"/>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
         <is>
           <t>(Senior) Corporate Counsel (m/w/d)</t>
         </is>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="E164" t="n">
+        <v>50</v>
+      </c>
+      <c r="F164" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000140933859</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr"/>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
         <is>
           <t>(Junior) Technical Project Manager – Events &amp; Exhibits</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="E165" t="n">
+        <v>50</v>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000137106040</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr"/>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
         <is>
           <t>Senior Group Reporting &amp; Accounting Policies (m/w/d)</t>
         </is>
       </c>
-      <c r="E166" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="E166" t="n">
+        <v>50</v>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000136443709</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr"/>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
         <is>
           <t>HR Payroll Specialist (m/w/d)</t>
         </is>
       </c>
-      <c r="E167" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="E167" t="n">
+        <v>50</v>
+      </c>
+      <c r="F167" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000135740449</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr"/>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
         <is>
           <t>Product Manager - Spine Surgery</t>
         </is>
       </c>
-      <c r="E168" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="E168" t="n">
+        <v>50</v>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000135719749</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr"/>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>(Junior) Area Account Manager (m/w/d) Schweiz</t>
         </is>
       </c>
-      <c r="E169" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="E169" t="n">
+        <v>50</v>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>Zürich, ch</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000134831479</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr"/>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
         <is>
           <t>Senior Accountant (m/w/d)</t>
         </is>
       </c>
-      <c r="E170" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="E170" t="n">
+        <v>50</v>
+      </c>
+      <c r="F170" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000132183599</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr"/>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
         <is>
           <t>Working Student - Mixed Reality Developer (Godot/C++)</t>
         </is>
       </c>
-      <c r="E171" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="E171" t="n">
+        <v>50</v>
+      </c>
+      <c r="F171" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000131687160</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr"/>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
         <is>
           <t>Manager Product Management - Integrated OR</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="E172" t="n">
+        <v>50</v>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000131677110</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr"/>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
         <is>
           <t xml:space="preserve">Buchhalter:in  </t>
         </is>
       </c>
-      <c r="E173" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="E173" t="n">
+        <v>50</v>
+      </c>
+      <c r="F173" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000131677598</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr"/>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
         <is>
           <t xml:space="preserve">(Senior) Project Engineer - Surgical Navigation Platforms </t>
         </is>
       </c>
-      <c r="E174" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="E174" t="n">
+        <v>50</v>
+      </c>
+      <c r="F174" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000129775149</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr"/>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
         <is>
           <t>Working Student Digital Learning –  R&amp;D Product Support</t>
         </is>
       </c>
-      <c r="E175" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="E175" t="n">
+        <v>50</v>
+      </c>
+      <c r="F175" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000122441969</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr"/>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
         <is>
           <t xml:space="preserve">(Senior) Software Engineer – Radiotherapy Positioning &amp; Monitoring </t>
         </is>
       </c>
-      <c r="E176" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="E176" t="n">
+        <v>50</v>
+      </c>
+      <c r="F176" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000120639709</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr"/>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
         <is>
           <t>Accounting Assistant (m/w/d)</t>
         </is>
       </c>
-      <c r="E177" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="E177" t="n">
+        <v>50</v>
+      </c>
+      <c r="F177" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000112601494</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr"/>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>TWAICE</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
         <is>
           <t>Working Student | Accounting &amp; Finance (m/f/d)</t>
         </is>
       </c>
-      <c r="E178" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="E178" t="n">
+        <v>50</v>
+      </c>
+      <c r="F178" t="inlineStr">
         <is>
           <t>Munich, Hybrid</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>https://twaice.jobs.personio.de/job/2779072</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr"/>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Blickfeld</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
         <is>
           <t>Initiativbewerbung</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="E179" t="n">
+        <v>50</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
         <is>
           <t>https://blickfeld.jobs.personio.de/job/128278</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr"/>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Blickfeld</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
         <is>
           <t>Mitarbeiter in der Auftrags- und Bestellabwicklung in Teilzeit (m/w/d)</t>
         </is>
       </c>
-      <c r="E180" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="E180" t="n">
+        <v>50</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
         <is>
           <t>https://blickfeld.jobs.personio.de/job/2780642</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr"/>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Blickfeld</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
         <is>
           <t>Werkstudent*in / IDP: Software Development (m/f/d)</t>
         </is>
       </c>
-      <c r="E181" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="E181" t="n">
+        <v>50</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>https://blickfeld.jobs.personio.de/job/2595961</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr"/>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
         <is>
           <t>Supply Chain Analyst (f/m/d)</t>
         </is>
       </c>
-      <c r="E182" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="E182" t="n">
+        <v>50</v>
+      </c>
+      <c r="F182" t="inlineStr">
         <is>
           <t>Supply Chain Analyst (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/c77fe49e-c58d-42bb-8a4a-c0c3517e0e9a</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr"/>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
         <is>
           <t>Working Student – BMS Software Testing (f/m/d)</t>
         </is>
       </c>
-      <c r="E183" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="E183" t="n">
+        <v>50</v>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>...tudent – BMS Software Testing (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/cfa18a3c-71f8-4f84-b28b-0412cdfee5a0</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr"/>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
         <is>
           <t>Product Owner Hardware (Bauteilverantwortliche*r) - (f/m/d)</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="E184" t="n">
+        <v>50</v>
+      </c>
+      <c r="F184" t="inlineStr">
         <is>
           <t>...(Bauteilverantwortliche*r) - (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/e722087a-6129-4366-a638-d68814de2e3c</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr"/>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
         <is>
           <t>Senior Embedded Software Engineer (C++) (f/m/d)</t>
         </is>
       </c>
-      <c r="E185" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="E185" t="n">
+        <v>50</v>
+      </c>
+      <c r="F185" t="inlineStr">
         <is>
           <t>...edded Software Engineer (C++) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/6c052597-f8b6-4ed0-b311-a3308998bc2a</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr"/>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
         <is>
           <t>Program Planning Manager - Development  (f/m/d)</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="E186" t="n">
+        <v>50</v>
+      </c>
+      <c r="F186" t="inlineStr">
         <is>
           <t>...anning Manager - Development  (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/d820a75d-1486-486f-bcd3-0a02f05b08c3</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr"/>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
         <is>
           <t>Engineering Manager - Software and System Testing (f/m/d)</t>
         </is>
       </c>
-      <c r="E187" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="E187" t="n">
+        <v>50</v>
+      </c>
+      <c r="F187" t="inlineStr">
         <is>
           <t>...- Software and System Testing (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/4472cec3-8839-4e87-b9ee-7abe91421589</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr"/>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
         <is>
           <t>Hardware Development Engineer (f/m/d)</t>
         </is>
       </c>
-      <c r="E188" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="E188" t="n">
+        <v>50</v>
+      </c>
+      <c r="F188" t="inlineStr">
         <is>
           <t>Hardware Development Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/321bfc57-ff1f-4288-98fc-af59a3d0fdf6</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr"/>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
         <is>
           <t>Senior Supplier Quality Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="E189" t="n">
+        <v>50</v>
+      </c>
+      <c r="F189" t="inlineStr">
         <is>
           <t>...nior Supplier Quality Manager (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G189" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/d15c6ed6-1880-4ba9-a9b1-85fc2c371d40</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr"/>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
         <is>
           <t>Senior Test Engineer (f/m/d)</t>
         </is>
       </c>
-      <c r="E190" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="E190" t="n">
+        <v>50</v>
+      </c>
+      <c r="F190" t="inlineStr">
         <is>
           <t>Senior Test Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/f731d4d8-1f65-45f3-b6ba-e2316adac453</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr"/>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
         <is>
           <t>Principal Software Engineer (C/C++) (f/m/d)</t>
         </is>
       </c>
-      <c r="E191" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="E191" t="n">
+        <v>50</v>
+      </c>
+      <c r="F191" t="inlineStr">
         <is>
           <t>...pal Software Engineer (C/C++) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/5b6595f3-389f-401e-b308-c8f6ae49ddb6</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr"/>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
         <is>
           <t>AI Platform Engineer (f/m/d)</t>
         </is>
       </c>
-      <c r="E192" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="E192" t="n">
+        <v>50</v>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>AI Platform Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/ba1a138b-d85a-45ea-b560-e0e7ffcce356</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr"/>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
         <is>
           <t>(Senior) Hardware Design Engineer (f/m/d)</t>
         </is>
       </c>
-      <c r="E193" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="E193" t="n">
+        <v>50</v>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>...ior) Hardware Design Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/9fa9670f-6c59-4510-96d8-de7104a23705</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr"/>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
         <is>
           <t>Functional Safety &amp; Cybersecurity Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="E194" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="E194" t="n">
+        <v>50</v>
+      </c>
+      <c r="F194" t="inlineStr">
         <is>
           <t>...afety &amp; Cybersecurity Manager (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/8bf45b4f-ecd1-4143-8ea8-7d5afc9ae8f4</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr"/>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
         <is>
           <t>Working Student – Battery Science and Data (f/m/d)</t>
         </is>
       </c>
-      <c r="E195" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="E195" t="n">
+        <v>50</v>
+      </c>
+      <c r="F195" t="inlineStr">
         <is>
           <t>...nt – Battery Science and Data (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/01c68b95-023d-476e-8b2d-654b5ffc7581</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr"/>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
         <is>
           <t>Product Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="E196" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="E196" t="n">
+        <v>50</v>
+      </c>
+      <c r="F196" t="inlineStr">
         <is>
           <t>Product Manager (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G196" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/e94ef6e0-6c2d-4901-a931-32b772b1bc62</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr"/>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
         <is>
           <t>Software Product Owner (f/m/d)</t>
         </is>
       </c>
-      <c r="E197" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="E197" t="n">
+        <v>50</v>
+      </c>
+      <c r="F197" t="inlineStr">
         <is>
           <t>Software Product Owner (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/7a10f170-0636-4601-af80-1923a9af588c</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr"/>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
         <is>
           <t>Inhouse Technical Recruiter (temporary contract for 1 year) (f/m/d)</t>
         </is>
       </c>
-      <c r="E198" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="E198" t="n">
+        <v>50</v>
+      </c>
+      <c r="F198" t="inlineStr">
         <is>
           <t>...emporary contract for 1 year) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/51e71582-de42-40b9-ab1c-33cadc119bcb</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr"/>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
         <is>
           <t>Field Application Engineer – Battery Management Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E199" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="E199" t="n">
+        <v>50</v>
+      </c>
+      <c r="F199" t="inlineStr">
         <is>
           <t>...– Battery Management Systems (m/f/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/afae4447-3a1a-41d1-b864-dda39992c320</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr"/>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
         <is>
           <t>Senior Embedded Software Developer (C) (f/m/d)</t>
         </is>
       </c>
-      <c r="E200" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="E200" t="n">
+        <v>50</v>
+      </c>
+      <c r="F200" t="inlineStr">
         <is>
           <t>...bedded Software Developer (C) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/c14b725d-cfee-4953-95ae-d129cd928ded</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr"/>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
         <is>
           <t>Test System Technician (f/m/d)</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="E201" t="n">
+        <v>50</v>
+      </c>
+      <c r="F201" t="inlineStr">
         <is>
           <t>Test System Technician (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G201" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/44e2b5e8-8734-44e0-9409-56d1c4e2a663</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr"/>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
         <is>
           <t>Design Quality Engineer (f/m/d)</t>
         </is>
       </c>
-      <c r="E202" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="E202" t="n">
+        <v>50</v>
+      </c>
+      <c r="F202" t="inlineStr">
         <is>
           <t>Design Quality Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/716b8f7a-dc69-41d9-acb2-1ccfd83a4fcd</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr"/>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
         <is>
           <t>IT Cloud Administrator (f/m/d)</t>
         </is>
       </c>
-      <c r="E203" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="E203" t="n">
+        <v>50</v>
+      </c>
+      <c r="F203" t="inlineStr">
         <is>
           <t>IT Cloud Administrator (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/1f17fad1-7d8e-4355-9bc3-9aedd7e283c4</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr"/>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
         <is>
           <t>Working Student – Software Development (f/m/d)</t>
         </is>
       </c>
-      <c r="E204" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="E204" t="n">
+        <v>50</v>
+      </c>
+      <c r="F204" t="inlineStr">
         <is>
           <t>...tudent – Software Development (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/6a466d9a-f1fd-4537-a879-4062857eb8c7</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr"/>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
         <is>
           <t>Putzhilfe/Reinigungskraft (f/m/d)</t>
         </is>
       </c>
-      <c r="E205" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="E205" t="n">
+        <v>50</v>
+      </c>
+      <c r="F205" t="inlineStr">
         <is>
           <t>Putzhilfe/Reinigungskraft (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/bcc4cef8-4e5f-4613-a355-d2b0f30e3bf4</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr"/>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
         <is>
           <t>Hausmeister/Facility Manager Assistant (f/m/d)</t>
         </is>
       </c>
-      <c r="E206" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="E206" t="n">
+        <v>50</v>
+      </c>
+      <c r="F206" t="inlineStr">
         <is>
           <t>...er/Facility Manager Assistant (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/a3263557-3de5-4760-b353-4750aab7da80</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr"/>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
         <is>
           <t>Manufacturing Technology Engineer (f/m/d)</t>
         </is>
       </c>
-      <c r="E207" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="E207" t="n">
+        <v>50</v>
+      </c>
+      <c r="F207" t="inlineStr">
         <is>
           <t>...facturing Technology Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/e536a980-8091-4c80-9f43-ea3eb9372c1b</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr"/>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
         <is>
           <t>NPI manager - Product Lifecycle Management (PLM) (f/m/d)</t>
         </is>
       </c>
-      <c r="E208" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="E208" t="n">
+        <v>50</v>
+      </c>
+      <c r="F208" t="inlineStr">
         <is>
           <t>...ct Lifecycle Management (PLM) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/1ea0166b-fd1c-4638-9927-ed448388ea35</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr"/>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
         <is>
           <t>Working Student / Intern - Hardware Validation (f/m/d)</t>
         </is>
       </c>
-      <c r="E209" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="E209" t="n">
+        <v>50</v>
+      </c>
+      <c r="F209" t="inlineStr">
         <is>
           <t>...Intern - Hardware Validation (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/0c10458a-38c3-404d-a923-7c231f781b1a</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr"/>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
         <is>
           <t>Lead Accounting &amp; Tax (f/m/d)</t>
         </is>
       </c>
-      <c r="E210" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="E210" t="n">
+        <v>50</v>
+      </c>
+      <c r="F210" t="inlineStr">
         <is>
           <t>Lead Accounting &amp; Tax (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/28766943-5082-43c4-b983-b413097a5f63</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr"/>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
         <is>
           <t>Working Student - Microfactory (f/m/d)</t>
         </is>
       </c>
-      <c r="E211" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="E211" t="n">
+        <v>50</v>
+      </c>
+      <c r="F211" t="inlineStr">
         <is>
           <t>...orking Student - Microfactory (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/f4d4c43d-d727-48c9-a5e6-ae95e6b16266</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr"/>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
         <is>
           <t xml:space="preserve">Head of Program Management (f/m/d) </t>
         </is>
       </c>
-      <c r="E212" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="E212" t="n">
+        <v>50</v>
+      </c>
+      <c r="F212" t="inlineStr">
         <is>
           <t>Head of Program Management (f/m/d)  @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/892df0b0-92f4-4587-8a7f-c0c4625831ef</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr"/>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
         <is>
           <t>Technical Lead Hardware Design (f/m/d)</t>
         </is>
       </c>
-      <c r="E213" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="E213" t="n">
+        <v>50</v>
+      </c>
+      <c r="F213" t="inlineStr">
         <is>
           <t>...echnical Lead Hardware Design (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/c4228b51-a553-45f2-9e32-07adda11a862</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr"/>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Scandit</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Computer Vision Engineer (Action Recognition) </t>
         </is>
       </c>
-      <c r="E214" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="E214" t="n">
+        <v>50</v>
+      </c>
+      <c r="F214" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>https://www.scandit.com/careers/job-description/?gh_jid=7588975</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +478,3848 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer -  3D Computer Vision</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4911999101?gh_jid=4911999101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - AI Safety</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4334849101?gh_jid=4334849101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer -  Computer Vision</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4334842101?gh_jid=4334842101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - Foundation Models</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4766708101?gh_jid=4766708101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T06:31:15-04:00</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - GPU Simulation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin - London - Paris</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4953387101?gh_jid=4953387101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - ML Engineering</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4778869101?gh_jid=4778869101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - ML &amp; Signal Processing</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4372802101?gh_jid=4372802101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona; Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4676357101?gh_jid=4676357101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:11-04:00</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Intern (PhD) – 3D Computer Vision</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona; Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4941957101?gh_jid=4941957101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:16-04:00</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Avionics Hardware Engineer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4878635101?gh_jid=4878635101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:25:27-04:00</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camera Engineer </t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4939591101?gh_jid=4939591101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:11-04:00</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4516967101?gh_jid=4516967101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T08:43:11-04:00</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Design Engineer - Electronics</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4660594101?gh_jid=4660594101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:11-04:00</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Drone Field Engineer</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4390825101?gh_jid=4390825101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:15-04:00</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Finance Data Engineer</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4871604101?gh_jid=4871604101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:17-04:00</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead Engineer – Ground Control Station (GCS) &amp; Hardware Simulator </t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4899205101?gh_jid=4899205101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:17-04:00</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Active RF Sensing</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4900888101?gh_jid=4900888101</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:07:30-04:00</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead Systems Engineer - Avionics Communication </t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4879138101?gh_jid=4879138101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - EO/IR Sensing</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4782393101?gh_jid=4782393101</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - LO Emission Control &amp; RF Interoperability</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4782354101?gh_jid=4782354101</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T09:55:28-04:00</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Low Observability Shaping &amp; Materials</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4844205101?gh_jid=4844205101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:17-04:00</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Maritime</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4908213101?gh_jid=4908213101</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:18-04:00</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer – Military Communications</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924405101?gh_jid=4924405101</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:16-04:00</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Lead Systems Engineer - Passive RF Sensing</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4888238101?gh_jid=4888238101</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T03:30:08-04:00</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LSA Engineer </t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4948287101?gh_jid=4948287101</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:18-04:00</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multimodal Sensing and Fusion Engineer </t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4938743101?gh_jid=4938743101</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:19-04:00</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multimodal Sensing Test Engineer </t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4947489101?gh_jid=4947489101</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:12-04:00</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Production Engineer - Software Integration</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4788891101?gh_jid=4788891101</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:15-04:00</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager — Electronic Warfare (Offboard &amp; Cross-Platform)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4869481101?gh_jid=4869481101</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:15-04:00</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Assurance Engineer - Development </t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4872445101?gh_jid=4872445101</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:18-04:00</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Radio Engineer</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4921704101?gh_jid=4921704101</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:16-04:00</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF &amp; EMC Engineer </t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4878616101?gh_jid=4878616101</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:15-04:00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Lead Engineer Electronic Warfare and Survivability </t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4870670101?gh_jid=4870670101</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:18-04:00</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Systems Engineer – EA Antenna &amp; Payload Design </t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924427101?gh_jid=4924427101</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:45:15-04:00</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer ESM / ELS</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924407101?gh_jid=4924407101</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Systems Safety Engineer - Air</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4776546101?gh_jid=4776546101</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:18-04:00</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Systems Safety Engineer - Land</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4924017101?gh_jid=4924017101</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:19-04:00</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Simulation Engineer</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4948430101?gh_jid=4948430101</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:11-04:00</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4347030101?gh_jid=4347030101</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4737931101?gh_jid=4737931101</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Airborne Mission Systems</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741565101?gh_jid=4741565101</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Autonomous Air Systems</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741571101?gh_jid=4741571101</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Autonomous Air System V&amp;V</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741219101?gh_jid=4741219101</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4125061101?gh_jid=4125061101</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:11-04:00</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Frontend</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin - London</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4126378101?gh_jid=4126378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Frontend Autonomous Air System V&amp;V</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741224101?gh_jid=4741224101</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Ground to Air HMI</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741242101?gh_jid=4741242101</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:10-04:00</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff Software Engineer </t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4923741101?gh_jid=4923741101</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:16-04:00</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Stress &amp; Dynamics Engineer</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4876328101?gh_jid=4876328101</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Systems Architect - Electronic Warfare</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4782364101?gh_jid=4782364101</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:17-04:00</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer (Avionics)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4902679101?gh_jid=4902679101</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:13-04:00</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Command and Control (Air)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4787205101?gh_jid=4787205101</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:15-04:00</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Electromagnetic Interference (EMI)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4865559101?gh_jid=4865559101</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:14-04:00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Physical Products</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4839745101?gh_jid=4839745101</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T02:03:36-04:00</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer (Requirements Manager), Aviation</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4871824101?gh_jid=4871824101</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:12-04:00</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer V&amp;V - Air</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4813822101?gh_jid=4813822101</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:16-04:00</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Technical Lead Engineer, UAV Development</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4888975101?gh_jid=4888975101</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:41:18-04:00</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Wireless Communications Systems Engineer</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4923845101?gh_jid=4923845101</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate (AI) Solution Consultant - Orbit Program </t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7814021003?gh_jid=7814021003</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Associate Applied (AI) Value Engineer (DACH) - Orbit Program</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7819725003?gh_jid=7819725003</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Client Engagement Partner - AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany, Cologne</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820049003?gh_jid=7820049003</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Client Engagement Partner - AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7777097003?gh_jid=7777097003</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner- AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7777096003?gh_jid=7777096003</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Client Value Partner- AI-Driven Transformation &amp; Process Intelligence (Logistics/Transportation)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Remote, Germany, Cologne</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820050003?gh_jid=7820050003</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise AI Consultant</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7972958003?gh_jid=7972958003</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Architect Director</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Zürich, Switzerland</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7693178003?gh_jid=7693178003</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Architect Director</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7681585003?gh_jid=7681585003</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Lead Cloud Economics Specialist</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7802410003?gh_jid=7802410003</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Lead Deployment Architect</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7727306003?gh_jid=7727306003</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Lead Deployment Architect - AI</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7928952003?gh_jid=7928952003</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Lead / Principal Consultant - Data and AI</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7926567003?gh_jid=7926567003</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Lead / Principal Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683435003?gh_jid=7683435003</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:13:09-04:00</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Lead/Principal Value Engineer - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7773834003?gh_jid=7773834003</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Lead Value Engineer - Insurance</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7828363003?gh_jid=7828363003</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Principal Enterprise Architect </t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7539075003?gh_jid=7539075003</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Application Product Manager - Supply Chain - Procurement </t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7984249003?gh_jid=7984249003</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Senior Applied Value Engineer</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7825688003?gh_jid=7825688003</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Senior Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Zürich, Switzerland</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7600347003?gh_jid=7600347003</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Design Engineer, Design System </t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7799733003?gh_jid=7799733003</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:03:57-04:00</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant (Senior Value Engineer) - Scale Team</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7826212003?gh_jid=7826212003</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Context Model Core Team</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820412003?gh_jid=7820412003</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:07:03-04:00</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Senior Value Engineer - Manufacturing/Production</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7825970003?gh_jid=7825970003</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:03:59-04:00</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Senior Value Engineer - Scale Team</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7817387003?gh_jid=7817387003</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:33:17-04:00</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer - Context Model Core Team</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820430003?gh_jid=7820430003</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Personio</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>https://personio.jobs.personio.de/job/1834171</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:05:56.953Z</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Business Application Engineer – Polarion ALM</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000144263839</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T06:08:54.016Z</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Area Product Owner Business Development - RT Elements</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000141845300</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T12:19:18.360Z</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager - Spine Surgery</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000135719749</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T14:12:45.627Z</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Working Student - Mixed Reality Developer (Godot/C++)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000131687160</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:07:00.757Z</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Senior) Project Engineer - Surgical Navigation Platforms </t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000129775149</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14T09:00:50.685Z</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Senior) Software Engineer – Radiotherapy Positioning &amp; Monitoring </t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000120639709</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Blickfeld</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent*in / IDP: Software Development (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>https://blickfeld.jobs.personio.de/job/2595961</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-17T10:00:36.504+00:00</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Working Student – BMS Software Testing (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>...tudent – BMS Software Testing (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/cfa18a3c-71f8-4f84-b28b-0412cdfee5a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:22.707+00:00</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Product Owner Hardware (Bauteilverantwortliche*r) - (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>...(Bauteilverantwortliche*r) - (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/e722087a-6129-4366-a638-d68814de2e3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:09.601+00:00</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Engineer (C++) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>...edded Software Engineer (C++) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/6c052597-f8b6-4ed0-b311-a3308998bc2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T16:30:40.371+00:00</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Software and System Testing (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>...- Software and System Testing (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/4472cec3-8839-4e87-b9ee-7abe91421589</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:05.356+00:00</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Development Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Development Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/321bfc57-ff1f-4288-98fc-af59a3d0fdf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:53.863+00:00</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Senior Test Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Senior Test Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/f731d4d8-1f65-45f3-b6ba-e2316adac453</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:53.615+00:00</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer (C/C++) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>...pal Software Engineer (C/C++) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/5b6595f3-389f-401e-b308-c8f6ae49ddb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T10:38:00.389+00:00</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/ba1a138b-d85a-45ea-b560-e0e7ffcce356</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:05.611+00:00</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Hardware Design Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>...ior) Hardware Design Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/9fa9670f-6c59-4510-96d8-de7104a23705</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:23.139+00:00</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/e94ef6e0-6c2d-4901-a931-32b772b1bc62</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26T15:18:08.294+00:00</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Software Product Owner (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Software Product Owner (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/7a10f170-0636-4601-af80-1923a9af588c</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T06:52:32.155+00:00</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Field Application Engineer – Battery Management Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>...– Battery Management Systems (m/f/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/afae4447-3a1a-41d1-b864-dda39992c320</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:01:54.001+00:00</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Developer (C) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>...bedded Software Developer (C) (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/c14b725d-cfee-4953-95ae-d129cd928ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19T12:29:01.846+00:00</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Design Quality Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Design Quality Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/716b8f7a-dc69-41d9-acb2-1ccfd83a4fcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02T16:14:29.953+00:00</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>IT Cloud Administrator (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>IT Cloud Administrator (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/1f17fad1-7d8e-4355-9bc3-9aedd7e283c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:24:13.412+00:00</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Working Student – Software Development (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>...tudent – Software Development (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/6a466d9a-f1fd-4537-a879-4062857eb8c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-05T13:53:25.912+00:00</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing Technology Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>...facturing Technology Engineer (f/m/d) @ Munich Electrification You need to enable JavaScript to run...</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/e536a980-8091-4c80-9f43-ea3eb9372c1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:56:55-04:00</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Scandit</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Computer Vision Engineer (Action Recognition) </t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.scandit.com/careers/job-description/?gh_jid=7588975</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +478,1258 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer -  3D Computer Vision</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4911999101?gh_jid=4911999101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - AI Safety</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4334849101?gh_jid=4334849101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer -  Computer Vision</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4334842101?gh_jid=4334842101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - Foundation Models</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4766708101?gh_jid=4766708101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - GPU Simulation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin - London - Paris</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4953387101?gh_jid=4953387101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - ML Engineering</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4778869101?gh_jid=4778869101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - ML &amp; Signal Processing</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4372802101?gh_jid=4372802101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Engineer - Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona; Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4676357101?gh_jid=4676357101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>AI Research Intern (PhD) – 3D Computer Vision</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona; Berlin; London; Munich; Paris</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4941957101?gh_jid=4941957101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4516967101?gh_jid=4516967101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Finance Data Engineer</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4871604101?gh_jid=4871604101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Production Engineer - Software Integration</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4788891101?gh_jid=4788891101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4737931101?gh_jid=4737931101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Airborne Mission Systems</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741565101?gh_jid=4741565101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Autonomous Air Systems</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741571101?gh_jid=4741571101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Autonomous Air System V&amp;V</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741219101?gh_jid=4741219101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4125061101?gh_jid=4125061101</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Frontend</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin - London</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4126378101?gh_jid=4126378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Frontend Autonomous Air System V&amp;V</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741224101?gh_jid=4741224101</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Ground to Air HMI</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4741242101?gh_jid=4741242101</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff Software Engineer </t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4923741101?gh_jid=4923741101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Lead Cloud Economics Specialist</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7802410003?gh_jid=7802410003</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Context Model Core Team</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820412003?gh_jid=7820412003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer - Context Model Core Team</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7820430003?gh_jid=7820430003</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Personio</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://personio.jobs.personio.de/job/1834171</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Brainlab</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Senior) Software Engineer – Radiotherapy Positioning &amp; Monitoring </t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Munich, de</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Brainlab/744000120639709</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Blickfeld</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent*in / IDP: Software Development (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://blickfeld.jobs.personio.de/job/2595961</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Working Student – BMS Software Testing (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/cfa18a3c-71f8-4f84-b28b-0412cdfee5a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Engineer (C++) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/6c052597-f8b6-4ed0-b311-a3308998bc2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Software and System Testing (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/4472cec3-8839-4e87-b9ee-7abe91421589</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer (C/C++) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/5b6595f3-389f-401e-b308-c8f6ae49ddb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/ba1a138b-d85a-45ea-b560-e0e7ffcce356</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Software Product Owner (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/7a10f170-0636-4601-af80-1923a9af588c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Developer (C) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/c14b725d-cfee-4953-95ae-d129cd928ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>IT Cloud Administrator (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/1f17fad1-7d8e-4355-9bc3-9aedd7e283c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Munich Electrification</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Working Student – Software Development (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/munich-electrification/6a466d9a-f1fd-4537-a879-4062857eb8c7</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -482,1252 +482,1250 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>AI Research Engineer -  3D Computer Vision</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4911999101?gh_jid=4911999101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>AI Research Engineer - AI Safety</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4334849101?gh_jid=4334849101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>AI Research Engineer -  Computer Vision</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4334842101?gh_jid=4334842101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>AI Research Engineer - Foundation Models</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4766708101?gh_jid=4766708101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>AI Research Engineer - GPU Simulation</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich - Berlin - London - Paris</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4953387101?gh_jid=4953387101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>AI Research Engineer - ML Engineering</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Berlin; London; Munich</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4778869101?gh_jid=4778869101</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>AI Research Engineer - ML &amp; Signal Processing</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4372802101?gh_jid=4372802101</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>AI Research Engineer - Reinforcement Learning</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Barcelona; Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4676357101?gh_jid=4676357101</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>AI Research Intern (PhD) – 3D Computer Vision</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Barcelona; Berlin; London; Munich; Paris</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4941957101?gh_jid=4941957101</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Deployed AI Engineer</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4516967101?gh_jid=4516967101</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Finance Data Engineer</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4871604101?gh_jid=4871604101</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Production Engineer - Software Integration</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4788891101?gh_jid=4788891101</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4737931101?gh_jid=4737931101</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Software Engineer - Airborne Mission Systems</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741565101?gh_jid=4741565101</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Software Engineer - Autonomous Air Systems</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741571101?gh_jid=4741571101</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Software Engineer - Autonomous Air System V&amp;V</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741219101?gh_jid=4741219101</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Software Engineer - Backend</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4125061101?gh_jid=4125061101</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Software Engineer - Frontend</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Munich - Berlin - London</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4126378101?gh_jid=4126378101</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Software Engineer - Frontend Autonomous Air System V&amp;V</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741224101?gh_jid=4741224101</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Software Engineer - Ground to Air HMI</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4741242101?gh_jid=4741242101</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">Staff Software Engineer </t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Berlin; London; Munich; Paris; Stockholm; Tallinn</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4923741101?gh_jid=4923741101</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Lead Cloud Economics Specialist</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7802410003?gh_jid=7802410003</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Senior Software Engineer - Context Model Core Team</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7820412003?gh_jid=7820412003</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Staff Software Engineer - Context Model Core Team</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="E25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7820430003?gh_jid=7820430003</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Personio</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Staff Software Engineer, Data Platform</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="E26" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://personio.jobs.personio.de/job/1834171</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Brainlab</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">(Senior) Software Engineer – Radiotherapy Positioning &amp; Monitoring </t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Munich, de</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Brainlab/744000120639709</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Blickfeld</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Werkstudent*in / IDP: Software Development (m/f/d)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://blickfeld.jobs.personio.de/job/2595961</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2025-12-17</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Working Student – BMS Software Testing (f/m/d)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/cfa18a3c-71f8-4f84-b28b-0412cdfee5a0</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Senior Embedded Software Engineer (C++) (f/m/d)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="E30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/6c052597-f8b6-4ed0-b311-a3308998bc2a</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Engineering Manager - Software and System Testing (f/m/d)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="E31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/4472cec3-8839-4e87-b9ee-7abe91421589</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Principal Software Engineer (C/C++) (f/m/d)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="E32" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/5b6595f3-389f-401e-b308-c8f6ae49ddb6</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>AI Platform Engineer (f/m/d)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="E33" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/ba1a138b-d85a-45ea-b560-e0e7ffcce356</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Software Product Owner (f/m/d)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="E34" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/7a10f170-0636-4601-af80-1923a9af588c</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Senior Embedded Software Developer (C) (f/m/d)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="E35" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/c14b725d-cfee-4953-95ae-d129cd928ded</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>IT Cloud Administrator (f/m/d)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/1f17fad1-7d8e-4355-9bc3-9aedd7e283c4</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Munich Electrification</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Working Student – Software Development (f/m/d)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="E37" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/munich-electrification/6a466d9a-f1fd-4537-a879-4062857eb8c7</t>
         </is>
